--- a/public/exports-60-250/41333014.xlsx
+++ b/public/exports-60-250/41333014.xlsx
@@ -3439,7 +3439,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311705508</t>
+          <t xml:space="preserve">311705435</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
